--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>business_date</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>Baay`isaa Kabbadaa</t>
+  </si>
+  <si>
+    <t>Mul`ataa Qajeelaa</t>
+  </si>
+  <si>
+    <t>Wasihun Geletu</t>
   </si>
 </sst>
 </file>
@@ -955,13 +961,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2220,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2232,6 +2239,88 @@
         <v>0</v>
       </c>
       <c r="M31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B32">
+        <v>1031</v>
+      </c>
+      <c r="C32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32">
+        <v>69000</v>
+      </c>
+      <c r="E32">
+        <v>40000</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>138000</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>2000</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B33">
+        <v>1032</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33">
+        <v>69000</v>
+      </c>
+      <c r="E33">
+        <v>3000</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>138000</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>2000</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J30">
         <v>0</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L16">
         <v>0</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1887,7 +1887,7 @@
         <v>69000</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F23">
         <v>1000</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>business_date</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Wasihun Geletu</t>
+  </si>
+  <si>
+    <t>Galaa Yaalii</t>
   </si>
 </sst>
 </file>
@@ -961,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2324,6 +2327,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B34">
+        <v>1033</v>
+      </c>
+      <c r="C34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34">
+        <v>69000</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>138000</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>2000</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -1029,7 +1029,7 @@
         <v>69000</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F2">
         <v>1000</v>
@@ -1070,7 +1070,7 @@
         <v>69000</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="F3">
         <v>1000</v>
@@ -1111,7 +1111,7 @@
         <v>69000</v>
       </c>
       <c r="E4">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="F4">
         <v>1000</v>
@@ -1152,7 +1152,7 @@
         <v>69000</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1193,7 +1193,7 @@
         <v>69000</v>
       </c>
       <c r="E6">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="F6">
         <v>1000</v>
@@ -1234,7 +1234,7 @@
         <v>69000</v>
       </c>
       <c r="E7">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="F7">
         <v>1000</v>
@@ -1275,7 +1275,7 @@
         <v>69000</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F8">
         <v>1000</v>
@@ -1316,7 +1316,7 @@
         <v>69000</v>
       </c>
       <c r="E9">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="F9">
         <v>1000</v>
@@ -1357,7 +1357,7 @@
         <v>69000</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F10">
         <v>1000</v>
@@ -1398,7 +1398,7 @@
         <v>69000</v>
       </c>
       <c r="E11">
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="F11">
         <v>1000</v>
@@ -1439,7 +1439,7 @@
         <v>69000</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F12">
         <v>1000</v>
@@ -1480,7 +1480,7 @@
         <v>69000</v>
       </c>
       <c r="E13">
-        <v>98000</v>
+        <v>101000</v>
       </c>
       <c r="F13">
         <v>1000</v>
@@ -1521,7 +1521,7 @@
         <v>69000</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F14">
         <v>1000</v>
@@ -1562,7 +1562,7 @@
         <v>69000</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F15">
         <v>1000</v>
@@ -1603,7 +1603,7 @@
         <v>69000</v>
       </c>
       <c r="E16">
-        <v>99000</v>
+        <v>104000</v>
       </c>
       <c r="F16">
         <v>1000</v>
@@ -1644,7 +1644,7 @@
         <v>69000</v>
       </c>
       <c r="E17">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>69000</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F18">
         <v>1000</v>
@@ -1726,7 +1726,7 @@
         <v>69000</v>
       </c>
       <c r="E19">
-        <v>73000</v>
+        <v>76000</v>
       </c>
       <c r="F19">
         <v>1000</v>
@@ -1767,7 +1767,7 @@
         <v>69000</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F20">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>69000</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F21">
         <v>1000</v>
@@ -1849,7 +1849,7 @@
         <v>69000</v>
       </c>
       <c r="E22">
-        <v>27000</v>
+        <v>42000</v>
       </c>
       <c r="F22">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
         <v>69000</v>
       </c>
       <c r="E23">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="F23">
         <v>1000</v>
@@ -1931,7 +1931,7 @@
         <v>69000</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F24">
         <v>1000</v>
@@ -1972,7 +1972,7 @@
         <v>69000</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F25">
         <v>1000</v>
@@ -2013,7 +2013,7 @@
         <v>69000</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F26">
         <v>1000</v>
@@ -2054,7 +2054,7 @@
         <v>69000</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F27">
         <v>1000</v>
@@ -2095,7 +2095,7 @@
         <v>69000</v>
       </c>
       <c r="E28">
-        <v>40000</v>
+        <v>43000</v>
       </c>
       <c r="F28">
         <v>1000</v>
@@ -2136,7 +2136,7 @@
         <v>69000</v>
       </c>
       <c r="E29">
-        <v>13000</v>
+        <v>40000</v>
       </c>
       <c r="F29">
         <v>1000</v>
@@ -2177,7 +2177,7 @@
         <v>69000</v>
       </c>
       <c r="E30">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F30">
         <v>1000</v>
@@ -2218,7 +2218,7 @@
         <v>69000</v>
       </c>
       <c r="E31">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F31">
         <v>1000</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>69000</v>
       </c>
       <c r="E32">
-        <v>40000</v>
+        <v>41000</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2300,7 +2300,7 @@
         <v>69000</v>
       </c>
       <c r="E33">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>69000</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F34">
         <v>0</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J31">
         <v>0</v>

--- a/EGSA2026_27_Plan_achie.xlsx
+++ b/EGSA2026_27_Plan_achie.xlsx
@@ -2177,7 +2177,7 @@
         <v>69000</v>
       </c>
       <c r="E30">
-        <v>3000</v>
+        <v>43000</v>
       </c>
       <c r="F30">
         <v>1000</v>
